--- a/data-downloads/bremerton_data.xlsx
+++ b/data-downloads/bremerton_data.xlsx
@@ -1201,7 +1201,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="14" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1"/>
